--- a/docs/测试用例/SynaRoute测试用例-2-Claude Code CLI.xlsx
+++ b/docs/测试用例/SynaRoute测试用例-2-Claude Code CLI.xlsx
@@ -11,7 +11,7 @@
     <sheet name="用例" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'用例'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'用例'!$A$1:$J$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -171,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -207,6 +213,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,7 +598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>版本 0.1.8    用例 23 条（其中 P0 必测 11 条）</t>
+          <t>版本 0.1.9    用例 26 条（其中 P0 必测 12 条）</t>
         </is>
       </c>
     </row>
@@ -763,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1906,16 +1915,156 @@
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="10" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>v0.1.9 本轮修复（真机测出，重点回归）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>聚合工具能读到项目文件（本轮 P0）</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>BrainPage 打开「工具调用」开关；成员里**包含一个 Claude 系模型**（如 claude-opus-4-8）；工作目录指向一个真实项目（建议含多层目录，如 Java 项目 src/main/java/...）</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>问一个「必须读多个文件才能回答」的问题，例如「这个项目的线程池是怎么配置的」</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>运行日志里 Claude 系成员的 read_file 调用应**成功**（不再是「被拒/失败」）；答案要引用具体文件内容。上一版的症状是该成员连续 8 次 read_file 全部失败、只能基于 pom.xml 之类泛泛作答</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>聚合运行日志（看有无「被拒/失败」）+ 答案是否引用了 .java 文件里的真实代码</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>工具参数别名兼容</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>同上，工具开关开启</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>多跑几次不同问法，观察日志里工具调用的参数名</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>无论模型发 path 还是 file_path / filePath / filename，都应执行成功；若发了别名之外的名字，错误提示里应列出可用的等价写法供模型改用</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>聚合运行日志的工具调用行</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>1M 上下文在 CLI 侧生效</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>CLI 分类主 Key 为 Anthropic 协议，模型窗口填 1000000，已接入并启动代理</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>在 Claude Code 里发一个长上下文会话（或直接看首次请求的头）</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>发往上游的 anthropic-beta 含 context-1m-2025-08-07。注意：客户端自己**不会**为我们的对外名发这个头，全靠代理补 —— 这条就是验代理补对了</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>运行日志链路快照里的请求头</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
-  <mergeCells count="4">
+  <autoFilter ref="A1:J32"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A7:J7"/>
     <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,失败,阻塞,跳过"</formula1>
     </dataValidation>
   </dataValidations>
